--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-pr-biobank-organization.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-pr-biobank-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-02</t>
+    <t>2026-09-10</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -602,7 +602,7 @@
     <t>beschreibung</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://fhir.bbmri-eric.eu/fhir/StructureDefinition/miabis-organization-description-extension}
+    <t xml:space="preserve">Extension {https://fhir.bbmri-eric.eu/StructureDefinition/miabis-organization-description-extension}
 </t>
   </si>
   <si>
@@ -619,14 +619,14 @@
     <t>collectionSetting</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://fhir.bbmri-eric.eu/fhir/StructureDefinition/miabis-sample-collection-setting-extension}
+    <t xml:space="preserve">Extension {https://fhir.bbmri-eric.eu/StructureDefinition/miabis-sample-collection-setting-extension}
 </t>
   </si>
   <si>
     <t>Sample Collection Setting Extension</t>
   </si>
   <si>
-    <t>The context in which the sample collection was/is conducted.</t>
+    <t>The context in which the Sample Collection was/is conducted.</t>
   </si>
   <si>
     <t>Organization.extension:collectionDesign</t>
@@ -635,7 +635,7 @@
     <t>collectionDesign</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://fhir.bbmri-eric.eu/fhir/StructureDefinition/miabis-collection-design-extension}
+    <t xml:space="preserve">Extension {https://fhir.bbmri-eric.eu/StructureDefinition/miabis-collection-design-extension}
 </t>
   </si>
   <si>
